--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Halaman /lokasi/{slug} langsung ada.</t>
+          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Kos bulanan di Batam. Status tiap kamar diperbarui langsung, jadi yang tampil kosong memang kosong.</t>
+          <t>Monthly rooms in Batam. Every room status is updated as it changes, so what shows as available really is available.</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Sepuluh menit jalan kaki ke Mega Mall dan Kantor Wali Kota, satu angkot ke pelabuhan feri Batam Centre. Bangunan tiga lantai dengan koridor terbuka dan pagar terkunci setelah jam sebelas malam.</t>
+          <t>A ten minute walk to Mega Mall and the mayor office, one minibus ride to the Batam Centre ferry terminal. Three floors, open corridors, and the gate is locked after eleven at night.</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Wi-Fi 200 Mbps, Dapur bersama, Mesin cuci, Parkir motor, Parkir mobil, CCTV 24 jam, Ruang jemur</t>
+          <t>Wi-Fi 200 Mbps, Shared kitchen, Washing machine, Motorbike parking, Car parking, CCTV around the clock, Drying area</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>Di gang belakang Nagoya Hill, dekat deretan kedai kopi dan tempat makan yang buka sampai dini hari. Cocok untuk yang kerja shift: koridor dan tangga berlampu sepanjang malam.</t>
+          <t>On the lane behind Nagoya Hill, next to the row of coffee shops and food stalls that stay open past midnight. Built for shift workers: the corridors and stairwells stay lit all night.</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Wi-Fi 100 Mbps, Dapur bersama, Mesin cuci, Parkir motor, CCTV 24 jam, Rooftop</t>
+          <t>Wi-Fi 100 Mbps, Shared kitchen, Washing machine, Motorbike parking, CCTV around the clock, Rooftop</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Paling dekat pintu depan</t>
+          <t>Closest to the front door</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Ditahan sampai 18 September</t>
+          <t>Held until 18 September</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, Kipas angin, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Jendela menghadap taman dalam</t>
+          <t>Window faces the inner garden</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Ditahan sampai 12 September</t>
+          <t>Held until 12 September</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Water heater, Pantry, Balkon</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Balkon menghadap Engku Putri</t>
+          <t>Balcony faces Engku Putri</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Water heater, Pantry, Balkon</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Water heater, Pantry, Balkon</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Kasur 120x200, Lemari, Meja belajar, Kursi, AC, Kamar mandi dalam</t>
+          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Ujung koridor, paling sepi</t>
+          <t>End of the corridor, the quietest one</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Ditahan sampai 20 September</t>
+          <t>Held until 20 September</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Akses langsung ke rooftop</t>
+          <t>Direct access to the rooftop</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Water heater, Kulkas kecil</t>
+          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">

--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Monthly rooms in Batam. Every room status is updated as it changes, so what shows as available really is available.</t>
+          <t>Kamar kos bulanan di Batam. Status tiap kamar diperbarui begitu berubah, jadi yang tampil tersedia memang benar-benar tersedia.</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>A ten minute walk to Mega Mall and the mayor office, one minibus ride to the Batam Centre ferry terminal. Three floors, open corridors, and the gate is locked after eleven at night.</t>
+          <t>Jalan kaki sepuluh menit ke Mega Mall dan kantor wali kota, sekali naik angkot ke pelabuhan feri Batam Centre. Tiga lantai, koridor terbuka, dan gerbang dikunci setelah pukul sebelas malam.</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Wi-Fi 200 Mbps, Shared kitchen, Washing machine, Motorbike parking, Car parking, CCTV around the clock, Drying area</t>
+          <t>Wi-Fi 200 Mbps, Dapur bersama, Mesin cuci, Parkir motor, Parkir mobil, CCTV 24 jam, Area jemur</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>On the lane behind Nagoya Hill, next to the row of coffee shops and food stalls that stay open past midnight. Built for shift workers: the corridors and stairwells stay lit all night.</t>
+          <t>Di gang belakang Nagoya Hill, bersebelahan dengan deretan kedai kopi dan warung makan yang buka sampai lewat tengah malam. Dibuat untuk pekerja shift: koridor dan tangga tetap terang sepanjang malam.</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Wi-Fi 100 Mbps, Shared kitchen, Washing machine, Motorbike parking, CCTV around the clock, Rooftop</t>
+          <t>Wi-Fi 100 Mbps, Dapur bersama, Mesin cuci, Parkir motor, CCTV 24 jam, Rooftop</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Closest to the front door</t>
+          <t>Paling dekat pintu depan</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Held until 18 September</t>
+          <t>Ditahan sampai 18 September</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Window faces the inner garden</t>
+          <t>Jendela menghadap taman dalam</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Held until 12 September</t>
+          <t>Ditahan sampai 12 September</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Balcony faces Engku Putri</t>
+          <t>Balkon menghadap Engku Putri</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>End of the corridor, the quietest one</t>
+          <t>Ujung koridor, paling tenang</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Held until 20 September</t>
+          <t>Ditahan sampai 20 September</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Direct access to the rooftop</t>
+          <t>Akses langsung ke rooftop</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">

--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -11,6 +11,7 @@
     <sheet name="config" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="lokasi" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="kamar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="denah" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -377,6 +378,41 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Panduan Kozy</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih dari dropdown. Harus sama persis dengan slug di tab lokasi.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Angka lantai, sama dengan kolom lantai di tab kamar.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Urutan baris di denah, dari depan ke belakang. 1, 2, 3, ...</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Isi kotak dari kiri ke kanan, dipisah koma. Boleh kode kamar (A1), kata kunci pintu / tangga / lift / lorong, tanda titik (.) untuk kotak kosong, atau tulisan bebas seperti WC atau Dapur.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Boleh dikosongkan. Isi di salah satu baris lantai: utara, selatan, timur, atau barat, yaitu arah yang menghadap ke atas denah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -666,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C39"/>
+  <dimension ref="B2:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -692,7 +728,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tiga tab yang dibaca website</t>
+          <t>Tab yang dibaca website</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -733,277 +769,369 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Mengubah status kamar</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
-        </is>
-      </c>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>denah</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Menggambar denah lantai (opsional)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Satu baris = satu baris denah</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
+          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Kolom sel</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Menambah tipe kamar</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
+          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Kata kunci</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Tulisan bebas</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Tidak ada tab tipe</t>
+          <t>arah</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Tulis sama persis</t>
+          <t>Salah ketik aman</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Samakan isinya</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Fasilitas dipotong</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Menambah lokasi</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
+          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Mengubah status kamar</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Menambah tipe kamar</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Tidak ada tab tipe</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Yang tidak boleh dilakukan</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
+          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Tulis sama persis</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Samakan isinya</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Jangan hapus baris</t>
+          <t>Fasilitas dipotong</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah baris 1</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah nama tab</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Tiga tab harus tetap bernama config, lokasi, dan kamar, huruf kecil.</t>
-        </is>
-      </c>
+          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Menambah lokasi</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Jangan cabut sharing</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Melihat angka terbaru</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
+          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Halaman lokasi</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Kalau ada yang aneh</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr"/>
+          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Yang tidak boleh dilakukan</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Jangan hapus baris</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Buka /purge</t>
+          <t>Jangan ubah baris 1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
+          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Jangan ubah nama tab</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Jangan cabut sharing</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Melihat angka terbaru</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Halaman lokasi</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Kalau ada yang aneh</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Buka /purge</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>Website tidak pernah kosong</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Kalau Sheet bermasalah, yang tampil adalah data terakhir yang tersimpan di kode.</t>
         </is>
@@ -2867,4 +2995,226 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>lokasi_slug</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>lantai</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>baris</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>sel</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>pintu, ., ., .</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>utara</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>A1, A2, A3, tangga</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>lorong, lorong, lorong, lorong</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>A4, A5, A6, lift</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>B1, B2, B3, WC</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>lorong, lorong, lorong, lorong</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>B4, B5, B6, tangga</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>lokasi!$A$2:$A$50</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"utara,selatan,timur,barat"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -11,6 +11,7 @@
     <sheet name="config" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="lokasi" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="kamar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="denah" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -377,6 +378,41 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Panduan Kozy</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Pilih dari dropdown. Harus sama persis dengan slug di tab lokasi.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Angka lantai, sama dengan kolom lantai di tab kamar.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Urutan baris di denah, dari depan ke belakang. 1, 2, 3, ...</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Isi kotak dari kiri ke kanan, dipisah koma. Boleh kode kamar (A1), kata kunci pintu / tangga / lift / lorong, tanda titik (.) untuk kotak kosong, atau tulisan bebas seperti WC atau Dapur.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Boleh dikosongkan. Isi di salah satu baris lantai: utara, selatan, timur, atau barat, yaitu arah yang menghadap ke atas denah.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -666,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C39"/>
+  <dimension ref="B2:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -692,7 +728,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tiga tab yang dibaca website</t>
+          <t>Tab yang dibaca website</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -733,277 +769,369 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Mengubah status kamar</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
-        </is>
-      </c>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>denah</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Menggambar denah lantai (opsional)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Satu baris = satu baris denah</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
+          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Kolom sel</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Menambah tipe kamar</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
+          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Kata kunci</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Tulisan bebas</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Tidak ada tab tipe</t>
+          <t>arah</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Tulis sama persis</t>
+          <t>Salah ketik aman</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Samakan isinya</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Fasilitas dipotong</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Menambah lokasi</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr"/>
+          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Mengubah status kamar</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Menambah tipe kamar</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Tidak ada tab tipe</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Yang tidak boleh dilakukan</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
+          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Tulis sama persis</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Samakan isinya</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Jangan hapus baris</t>
+          <t>Fasilitas dipotong</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah baris 1</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah nama tab</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Tiga tab harus tetap bernama config, lokasi, dan kamar, huruf kecil.</t>
-        </is>
-      </c>
+          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Menambah lokasi</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Jangan cabut sharing</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Melihat angka terbaru</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
+          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Halaman lokasi</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Kalau ada yang aneh</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr"/>
+          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Yang tidak boleh dilakukan</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Jangan hapus baris</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Buka /purge</t>
+          <t>Jangan ubah baris 1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
+          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Jangan ubah nama tab</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Jangan cabut sharing</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Melihat angka terbaru</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Halaman lokasi</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Kalau ada yang aneh</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Buka /purge</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>Website tidak pernah kosong</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Kalau Sheet bermasalah, yang tampil adalah data terakhir yang tersimpan di kode.</t>
         </is>
@@ -1062,7 +1190,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Monthly rooms in Batam. Every room status is updated as it changes, so what shows as available really is available.</t>
+          <t>Kamar kos bulanan di Batam. Status tiap kamar diperbarui begitu berubah, jadi yang tampil tersedia memang benar-benar tersedia.</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1336,12 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>A ten minute walk to Mega Mall and the mayor office, one minibus ride to the Batam Centre ferry terminal. Three floors, open corridors, and the gate is locked after eleven at night.</t>
+          <t>Jalan kaki sepuluh menit ke Mega Mall dan kantor wali kota, sekali naik angkot ke pelabuhan feri Batam Centre. Tiga lantai, koridor terbuka, dan gerbang dikunci setelah pukul sebelas malam.</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Wi-Fi 200 Mbps, Shared kitchen, Washing machine, Motorbike parking, Car parking, CCTV around the clock, Drying area</t>
+          <t>Wi-Fi 200 Mbps, Dapur bersama, Mesin cuci, Parkir motor, Parkir mobil, CCTV 24 jam, Area jemur</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -1265,12 +1393,12 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>On the lane behind Nagoya Hill, next to the row of coffee shops and food stalls that stay open past midnight. Built for shift workers: the corridors and stairwells stay lit all night.</t>
+          <t>Di gang belakang Nagoya Hill, bersebelahan dengan deretan kedai kopi dan warung makan yang buka sampai lewat tengah malam. Dibuat untuk pekerja shift: koridor dan tangga tetap terang sepanjang malam.</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Wi-Fi 100 Mbps, Shared kitchen, Washing machine, Motorbike parking, CCTV around the clock, Rooftop</t>
+          <t>Wi-Fi 100 Mbps, Dapur bersama, Mesin cuci, Parkir motor, CCTV 24 jam, Rooftop</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr"/>
@@ -1413,7 +1541,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -1423,7 +1551,7 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>Closest to the front door</t>
+          <t>Paling dekat pintu depan</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -1470,7 +1598,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1523,7 +1651,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1576,7 +1704,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1629,7 +1757,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1639,7 +1767,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Held until 18 September</t>
+          <t>Ditahan sampai 18 September</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1686,7 +1814,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Ceiling fan, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, Kipas angin plafon, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -1739,7 +1867,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1749,7 +1877,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Window faces the inner garden</t>
+          <t>Jendela menghadap taman dalam</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1796,7 +1924,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1849,7 +1977,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1902,7 +2030,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1955,7 +2083,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -2008,7 +2136,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -2018,7 +2146,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Held until 12 September</t>
+          <t>Ditahan sampai 12 September</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -2065,7 +2193,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2075,7 +2203,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>Balcony faces Engku Putri</t>
+          <t>Balkon menghadap Engku Putri</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -2122,7 +2250,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -2175,7 +2303,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Sofa, Air conditioning, Private bathroom, Water heater, Pantry, Balcony</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Sofa, AC, Kamar mandi dalam, Pemanas air, Pantry, Balkon</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -2228,7 +2356,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -2281,7 +2409,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -2334,7 +2462,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2387,7 +2515,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -2440,7 +2568,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -2493,7 +2621,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Bed 120x200, Wardrobe, Desk, Chair, Air conditioning, Private bathroom</t>
+          <t>Kasur 120x200, Lemari, Meja, Kursi, AC, Kamar mandi dalam</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -2503,7 +2631,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>End of the corridor, the quietest one</t>
+          <t>Ujung koridor, paling tenang</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -2550,7 +2678,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2603,7 +2731,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2613,7 +2741,7 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Held until 20 September</t>
+          <t>Ditahan sampai 20 September</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2660,7 +2788,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -2713,7 +2841,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2723,7 +2851,7 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Direct access to the rooftop</t>
+          <t>Akses langsung ke rooftop</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2770,7 +2898,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -2823,7 +2951,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Bed 160x200, Wardrobe, Work desk, Chair, Air conditioning, Private bathroom, Water heater, Mini fridge</t>
+          <t>Kasur 160x200, Lemari, Meja kerja, Kursi, AC, Kamar mandi dalam, Pemanas air, Kulkas mini</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -2867,4 +2995,226 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>lokasi_slug</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>lantai</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>baris</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>sel</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>pintu, ., ., .</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>utara</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>A1, A2, A3, tangga</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>lorong, lorong, lorong, lorong</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>A4, A5, A6, lift</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>B1, B2, B3, WC</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>lorong, lorong, lorong, lorong</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>batam-centre</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>B4, B5, B6, tangga</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>lokasi!$A$2:$A$50</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"utara,selatan,timur,barat"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C48"/>
+  <dimension ref="B2:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tab yang dibaca website</t>
+          <t>Link penting</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -736,402 +736,423 @@
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>Perbarui website</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Nama properti, kalimat perkenalan, nomor WhatsApp utama, dan alamat kantor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>lokasi</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Satu baris untuk satu bangunan kos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>kamar</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Satu baris untuk satu kamar fisik. Baris inilah yang jadi kotak di denah kamar.</t>
-        </is>
-      </c>
+          <t>https://namawebsite.netlify.app/purge?secret=GANTI_INI
+Ganti namawebsite dan GANTI_INI dengan URL dan rahasia yang diberikan developer. Simpan sebagai bookmark. Buka link ini setiap kali mengubah data di Sheet supaya perubahan langsung muncul. Tanpa dibuka pun perubahan muncul sendiri dalam 1–2 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tab yang dibaca website</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>denah</t>
+          <t>config</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Menggambar denah lantai (opsional)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>Nama properti, kalimat perkenalan, nomor WhatsApp utama, dan alamat kantor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>lokasi</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Satu baris untuk satu bangunan kos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>kamar</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Satu baris untuk satu kamar fisik. Baris inilah yang jadi kotak di denah kamar.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Satu baris = satu baris denah</t>
+          <t>denah</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Kolom sel</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Kata kunci</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
-        </is>
-      </c>
+          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Menggambar denah lantai (opsional)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tulisan bebas</t>
+          <t>Satu baris = satu baris denah</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>arah</t>
+          <t>Kolom sel</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
+          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Salah ketik aman</t>
+          <t>Kata kunci</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Mengubah status kamar</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
+          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Tulisan bebas</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>arah</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>Salah ketik aman</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Mengubah status kamar</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Menambah tipe kamar</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Tidak ada tab tipe</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Tulis sama persis</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Samakan isinya</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Menambah tipe kamar</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Fasilitas dipotong</t>
+          <t>Tidak ada tab tipe</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Menambah lokasi</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr"/>
+          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Tulis sama persis</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Samakan isinya</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Fasilitas dipotong</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
-        </is>
-      </c>
+          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Menambah lokasi</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Yang tidak boleh dilakukan</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr"/>
+          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Jangan hapus baris</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah baris 1</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah nama tab</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Yang tidak boleh dilakukan</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Jangan cabut sharing</t>
+          <t>Jangan hapus baris</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Melihat angka terbaru</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr"/>
+          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Jangan ubah baris 1</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Jangan ubah nama tab</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>Jangan cabut sharing</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Melihat angka terbaru</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Halaman lokasi</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Kalau ada yang aneh</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Halaman lokasi</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Kalau ada yang aneh</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>Buka /purge</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="4" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Website tidak pernah kosong</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Kalau Sheet bermasalah, yang tampil adalah data terakhir yang tersimpan di kode.</t>
         </is>

--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://namawebsite.netlify.app/purge?secret=GANTI_INI
+          <t>https://namawebsite.vercel.app/purge?secret=GANTI_INI
 Ganti namawebsite dan GANTI_INI dengan URL dan rahasia yang diberikan developer. Simpan sebagai bookmark. Buka link ini setiap kali mengubah data di Sheet supaya perubahan langsung muncul. Tanpa dibuka pun perubahan muncul sendiri dalam 1–2 menit.</t>
         </is>
       </c>

--- a/docs/kozy-sheet-template.xlsx
+++ b/docs/kozy-sheet-template.xlsx
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C48"/>
+  <dimension ref="B2:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tab yang dibaca website</t>
+          <t>Link penting</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -736,402 +736,423 @@
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>Perbarui website</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Nama properti, kalimat perkenalan, nomor WhatsApp utama, dan alamat kantor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>lokasi</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Satu baris untuk satu bangunan kos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>kamar</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Satu baris untuk satu kamar fisik. Baris inilah yang jadi kotak di denah kamar.</t>
-        </is>
-      </c>
+          <t>https://namawebsite.vercel.app/purge?secret=GANTI_INI
+Ganti namawebsite dan GANTI_INI dengan URL dan rahasia yang diberikan developer. Simpan sebagai bookmark. Buka link ini setiap kali mengubah data di Sheet supaya perubahan langsung muncul. Tanpa dibuka pun perubahan muncul sendiri dalam 1–2 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tab yang dibaca website</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>denah</t>
+          <t>config</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Menggambar denah lantai (opsional)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>Nama properti, kalimat perkenalan, nomor WhatsApp utama, dan alamat kantor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>lokasi</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Satu baris untuk satu bangunan kos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>kamar</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Satu baris untuk satu kamar fisik. Baris inilah yang jadi kotak di denah kamar.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Satu baris = satu baris denah</t>
+          <t>denah</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Kolom sel</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Kata kunci</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
-        </is>
-      </c>
+          <t>Opsional. Menggambar tata letak tiap lantai. Kalau dikosongkan, denah kamar tetap tampil sebagai daftar kotak per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Menggambar denah lantai (opsional)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tulisan bebas</t>
+          <t>Satu baris = satu baris denah</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+          <t>Di tab denah, isi lokasi_slug, lantai, dan baris (1, 2, 3 dari depan ke belakang).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>arah</t>
+          <t>Kolom sel</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
+          <t>Tulis isi kotak dari kiri ke kanan, dipisah koma. Contoh: A1, A2, lorong, A3, tangga.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Salah ketik aman</t>
+          <t>Kata kunci</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Mengubah status kamar</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
+          <t>pintu, tangga, lift, lorong tampil dengan ikon. Titik (.) berarti kotak kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Tulisan bebas</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Kata lain seperti WC atau Dapur tampil apa adanya sebagai penanda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>arah</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Boleh dikosongkan. Isi utara / selatan / timur / barat di salah satu baris lantai untuk menampilkan kompas.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>Salah ketik aman</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Kode kamar yang tidak dikenali tidak hilang, kamarnya muncul di bagian Belum dipetakan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Mengubah status kamar</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Buka tab kamar, cari baris kamarnya lewat kolom kode.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Ketuk kolom status, pilih kosong, dibooking, atau terisi dari dropdown.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Menambah tipe kamar</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Tidak ada tab tipe</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Tulis sama persis</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Samakan isinya</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Tanpa langkah ini pun perubahan muncul sendiri dalam 5 menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Menambah tipe kamar</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Fasilitas dipotong</t>
+          <t>Tidak ada tab tipe</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Menambah lokasi</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr"/>
+          <t>Tipe kamar terbentuk sendiri dari kolom tipe di tab kamar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Tulis sama persis</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Deluxe AC dan Deluxe A/C dianggap dua tipe berbeda. Pakai dropdown supaya seragam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Samakan isinya</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Harga, luas, dan fasilitas semua kamar bertipe sama sebaiknya diisi sama.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Fasilitas dipotong</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
-        </is>
-      </c>
+          <t>Kartu tipe hanya menampilkan fasilitas yang dimiliki SEMUA kamar bertipe itu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Menambah lokasi</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Yang tidak boleh dilakukan</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr"/>
+          <t>Tab lokasi, tambah baris. Isi minimal slug, nama, alamat, dan aktif = TRUE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Kolom nomor_wa boleh dikosongkan kalau lokasi ini memakai nomor utama di tab config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Tab kamar, tambah baris kamarnya. Kolom lokasi_slug pilih dari dropdown.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Jangan hapus baris</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah baris 1</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Jangan ubah nama tab</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
-        </is>
-      </c>
+          <t>Buka bookmark Perbarui website. Halaman /locations/{slug} langsung ada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Yang tidak boleh dilakukan</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Jangan cabut sharing</t>
+          <t>Jangan hapus baris</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Melihat angka terbaru</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr"/>
+          <t>Untuk menyembunyikan lokasi atau kamar, ubah kolom aktif menjadi FALSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Jangan ubah baris 1</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Nama kolom di baris pertama dipakai website untuk mengenali datanya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Jangan ubah nama tab</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>config, lokasi, dan kamar harus tetap bernama persis itu, huruf kecil. Tab denah opsional, tetapi kalau dipakai namanya juga harus denah.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>Jangan cabut sharing</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>File harus tetap Anyone with the link, Viewer. Kalau dicabut, website memakai data cadangan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Melihat angka terbaru</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Halaman depan menampilkan jumlah lokasi, total kamar kosong, dan harga terendah.</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Halaman lokasi</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Kalau ada yang aneh</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Halaman lokasi</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Denah kamar menampilkan status tiap kamar, dikelompokkan per lantai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Kalau ada yang aneh</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>Buka /purge</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Halaman itu menyebut sumber data yang sedang dipakai, jumlah baris terbaca, dan baris mana yang dilewati karena datanya belum lengkap.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="4" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Website tidak pernah kosong</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Kalau Sheet bermasalah, yang tampil adalah data terakhir yang tersimpan di kode.</t>
         </is>
